--- a/dummy_applicants.xlsx
+++ b/dummy_applicants.xlsx
@@ -419,22 +419,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>institution</t>
+          <t>Institution</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>Project</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Score</t>
         </is>
       </c>
     </row>
